--- a/data/trending_integrated_20260918_12.xlsx
+++ b/data/trending_integrated_20260918_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25800</v>
+        <v>25900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.44%</t>
+          <t>'+19.91%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -601,7 +601,7 @@
         <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>25950</v>
+        <v>26200</v>
       </c>
       <c r="M2" t="n">
         <v>21700</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>248592210050</v>
+        <v>256312327650</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 데이터센터 수혜 및 광통신 관련주 분석. 프로그램/외인 폭풍 매수 확인.</t>
+          <t>성호전자, AI 데이터센터 및 광통신 관련주로서의 폭발적인 프로그램 매수와 박스권 돌파.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '매수']</t>
+          <t>['AI', '광통신', '박스권']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8270</v>
+        <v>8320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.81%</t>
+          <t>'+18.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
         <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>138357379175</v>
+        <v>139575346970</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>연말 홀딩 및 10000원 돌파 기대감. 외국인/프로그램 매수 확인.</t>
+          <t>우리로, 홀딩 및 상한가 기대감 속 외국인 순매수 신호와 개인 투자자들의 차익 실현.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['홀딩', '매수', '기대감']</t>
+          <t>['홀딩', '상한가', '외국인']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18800</v>
+        <v>18870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.55%</t>
+          <t>'+16.99%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="F4" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G4" t="n">
-        <v>1677</v>
+        <v>1752</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -785,7 +785,7 @@
         <v>16360</v>
       </c>
       <c r="L4" t="n">
-        <v>18800</v>
+        <v>18870</v>
       </c>
       <c r="M4" t="n">
         <v>16170</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>614290272570</v>
+        <v>635555572540</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31500</v>
+        <v>31400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.31%</t>
+          <t>'+10.95%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H5" t="n">
         <v>11.44</v>
@@ -886,7 +886,7 @@
         <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>169715261200</v>
+        <v>172238248275</v>
       </c>
       <c r="P5" t="n">
         <v>75900</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속 저평가 해소 기대감. 박스권 상단 돌파 시도.</t>
+          <t>대한전선, 저평가 해소 및 박스권 상단 돌파 기대감 속 기관 순매수 신호.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['저평가', '박스권', '돌파']</t>
+          <t>['저평가', '박스권', '기관']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12820</v>
+        <v>12730</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.71%</t>
+          <t>'+9.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F6" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G6" t="n">
-        <v>482</v>
+        <v>505</v>
       </c>
       <c r="H6" t="n">
         <v>8.029999999999999</v>
@@ -978,7 +978,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>113945088240</v>
+        <v>116644681590</v>
       </c>
       <c r="P6" t="n">
         <v>21150</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>셀그램 관련 뉴스 기대감 속 단기 이익 실현 및 관망세. 외인/기관 동시 매수 확인.</t>
+          <t>파미셀, 모더나 관련 기대감 속 개인 투자자들의 엇갈린 전망과 투매 신호.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['셀그램', '뉴스', '매수세']</t>
+          <t>['셀그램', '투자전망', '주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6430</v>
+        <v>6410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.35%</t>
+          <t>'+9.01%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="H7" t="n">
         <v>2.85</v>
@@ -1070,7 +1070,7 @@
         <v>1.83</v>
       </c>
       <c r="O7" t="n">
-        <v>83047973370</v>
+        <v>84527837030</v>
       </c>
       <c r="P7" t="n">
         <v>11760</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>저평가 구간 해소 및 전환사채 발행 가능성. 외인/프로그램/기타 매수 확인.</t>
+          <t>KBI메탈, 변압기 관련주로서의 저평가 해소 및 전환사채 발행 후 상한가 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['저평가', '전환사채', '매수']</t>
+          <t>['변압기', '저평가', '전환사채']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14030</v>
+        <v>13970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.10%</t>
+          <t>'+8.63%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>129553658410</v>
+        <v>132006610955</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1825000</v>
+        <v>1832000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.58%</t>
+          <t>'+4.99%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="G9" t="n">
-        <v>2478</v>
+        <v>2273</v>
       </c>
       <c r="H9" t="n">
         <v>50.1</v>
@@ -1245,7 +1245,7 @@
         <v>1810000</v>
       </c>
       <c r="L9" t="n">
-        <v>1828000</v>
+        <v>1833000</v>
       </c>
       <c r="M9" t="n">
         <v>1805000</v>
@@ -1254,7 +1254,7 @@
         <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2417201732500</v>
+        <v>2652074578500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>반도체 수요 증가 및 외인 순매수 전환, 자사주 매입. 연말 500 예상.</t>
+          <t>SK하이닉스, 외인 순매수 전환 및 자사주 매입 시작에 따른 190만 돌파 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체', '외인매수', '자사주매입']</t>
+          <t>['외인매수', '자사주매입', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13860</v>
+        <v>13870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.98%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
         <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H10" t="n">
         <v>4.92</v>
@@ -1346,7 +1346,7 @@
         <v>4.99</v>
       </c>
       <c r="O10" t="n">
-        <v>52917119525</v>
+        <v>53951808665</v>
       </c>
       <c r="P10" t="n">
         <v>30200</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19130</v>
+        <v>11040</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.46%</t>
+          <t>'+4.05%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>344</v>
+        <v>133</v>
       </c>
       <c r="H11" t="n">
-        <v>10.74</v>
+        <v>12.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18490</v>
+        <v>10610</v>
       </c>
       <c r="K11" t="n">
-        <v>18900</v>
+        <v>10730</v>
       </c>
       <c r="L11" t="n">
-        <v>19700</v>
+        <v>12390</v>
       </c>
       <c r="M11" t="n">
-        <v>18770</v>
+        <v>10510</v>
       </c>
       <c r="N11" t="n">
-        <v>10.85</v>
+        <v>12.6</v>
       </c>
       <c r="O11" t="n">
-        <v>97928708900</v>
+        <v>102410846670</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>14350</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>465</v>
       </c>
       <c r="R11" t="n">
-        <v>392000</v>
+        <v>30000</v>
       </c>
       <c r="S11" t="n">
-        <v>106000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국장 및 중동 정세 관련 상승 기대감. 대차해지 운동 참여 독려.</t>
+          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차해지', '중동', '건설']</t>
+          <t>['주포', '호남반도체', '상한가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>259250</v>
+        <v>19070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.67%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>119</v>
       </c>
       <c r="F12" t="n">
-        <v>445</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
-        <v>2003</v>
+        <v>349</v>
       </c>
       <c r="H12" t="n">
-        <v>46.48</v>
+        <v>10.74</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>252500</v>
+        <v>18490</v>
       </c>
       <c r="K12" t="n">
-        <v>261000</v>
+        <v>18900</v>
       </c>
       <c r="L12" t="n">
-        <v>261000</v>
+        <v>19700</v>
       </c>
       <c r="M12" t="n">
-        <v>257500</v>
+        <v>18770</v>
       </c>
       <c r="N12" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1372406479000</v>
+        <v>100261823355</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>78600</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-601000</v>
+        <v>392000</v>
       </c>
       <c r="S12" t="n">
-        <v>333000</v>
+        <v>106000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치 관련 논쟁 지속, 주가 상승에 대한 부정적 전망.</t>
+          <t>미국장 및 중동 정세 관련 상승 기대감. 대차해지 운동 참여 독려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치', '기자회견', '신뢰']</t>
+          <t>['대차해지', '중동', '건설']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11370</v>
+        <v>260000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.97%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>70</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>445</v>
       </c>
       <c r="G13" t="n">
-        <v>124</v>
+        <v>2049</v>
       </c>
       <c r="H13" t="n">
-        <v>12.5</v>
+        <v>46.48</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>11080</v>
+        <v>252500</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>257500</v>
       </c>
       <c r="N13" t="n">
-        <v>12.6</v>
+        <v>46.52</v>
       </c>
       <c r="O13" t="n">
-        <v>98761000000</v>
+        <v>1491682652250</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>78600</v>
       </c>
       <c r="R13" t="n">
-        <v>30000</v>
+        <v>-601000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
+          <t>삼성전자, 정치적 발언이 주를 이루는 내용으로 특정 정치인에 대한 비판과 지지 혼재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,20 +1647,20 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주포', '호남반도체', '상한가']</t>
+          <t>['정치', '기자회견', '대통령']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52400</v>
+        <v>52600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.94%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="H14" t="n">
         <v>38.54</v>
@@ -1714,7 +1714,7 @@
         <v>38.62</v>
       </c>
       <c r="O14" t="n">
-        <v>186679131500</v>
+        <v>189130780250</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>외인 기관 매수세 확인, 개인 매도세 관찰.</t>
+          <t>삼성E&amp;A, 외인·기관 동시 매수세 속 상승 기대감과 개인 투자자들의 매도 관망세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인', '기관', '매수세']</t>
+          <t>['외인기관', '매수세', '상승전망']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15" t="n">
         <v>0.97</v>
@@ -1806,7 +1806,7 @@
         <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>69485230185</v>
+        <v>69732928295</v>
       </c>
       <c r="P15" t="n">
         <v>30550</v>
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13560</v>
+        <v>85600</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>217</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="G16" t="n">
-        <v>240</v>
+        <v>981</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>23.23</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13360</v>
+        <v>85400</v>
       </c>
       <c r="K16" t="n">
-        <v>13450</v>
+        <v>87300</v>
       </c>
       <c r="L16" t="n">
-        <v>14450</v>
+        <v>87800</v>
       </c>
       <c r="M16" t="n">
-        <v>13450</v>
+        <v>85300</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>23.27</v>
       </c>
       <c r="O16" t="n">
-        <v>33354666065</v>
+        <v>83895128000</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>139200</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>57000</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-206000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-59000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
+          <t>두산에너빌리티, 미국 원전주 급등에 따른 대미 투자 관련 발표 기대감 및 긍정적 주가 흐름.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['호남반도체', '실적', '급락']</t>
+          <t>['원전', '대미투자', '주가흐름']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>85600</v>
+        <v>13380</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.15%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>935</v>
+        <v>260</v>
       </c>
       <c r="H17" t="n">
-        <v>23.23</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85400</v>
+        <v>13360</v>
       </c>
       <c r="K17" t="n">
-        <v>87300</v>
+        <v>13450</v>
       </c>
       <c r="L17" t="n">
-        <v>87800</v>
+        <v>14450</v>
       </c>
       <c r="M17" t="n">
-        <v>85300</v>
+        <v>13350</v>
       </c>
       <c r="N17" t="n">
-        <v>23.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>81949118900</v>
+        <v>35272198710</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>19380</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>3200</v>
       </c>
       <c r="R17" t="n">
-        <v>-206000</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-59000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 증시 원전주 급등 및 대미 투자 관련 발표 가능성 뉴스를 기반으로 상승 기대감 형성. 다만, 구체적인 공시나 실적 발표보다는 소문과 기대에 기반한 분위기.</t>
+          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '뉴스']</t>
+          <t>['호남반도체', '실적', '급락']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17850</v>
+        <v>17920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.45%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.38</v>
       </c>
       <c r="E18" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F18" t="n">
         <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H18" t="n">
         <v>0.98</v>
@@ -2082,7 +2082,7 @@
         <v>0.6</v>
       </c>
       <c r="O18" t="n">
-        <v>72759950550</v>
+        <v>73653003550</v>
       </c>
       <c r="P18" t="n">
         <v>21100</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10290</v>
+        <v>10240</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.00%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>25760193975</v>
+        <v>28540248590</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4150</v>
+        <v>4145</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-10.46%</t>
+          <t>'-10.57%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="F20" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G20" t="n">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2260,13 +2260,13 @@
         <v>4535</v>
       </c>
       <c r="M20" t="n">
-        <v>4135</v>
+        <v>4125</v>
       </c>
       <c r="N20" t="n">
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>32473754969</v>
+        <v>33178513195</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
         <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>

--- a/data/trending_integrated_20260918_12.xlsx
+++ b/data/trending_integrated_20260918_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25900</v>
+        <v>26300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+19.91%</t>
+          <t>'+21.76%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -601,7 +601,7 @@
         <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>26200</v>
+        <v>26300</v>
       </c>
       <c r="M2" t="n">
         <v>21700</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>256312327650</v>
+        <v>262480817075</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>성호전자, AI 데이터센터 및 광통신 관련주로서의 폭발적인 프로그램 매수와 박스권 돌파.</t>
+          <t>성호전자, 박스권 상단 돌파 후 강한 상승세. 외인·프로그램 매수세 유입 속 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '박스권']</t>
+          <t>['박스권 돌파', '외인 매수', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8320</v>
+        <v>8300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.52%</t>
+          <t>'+18.23%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
         <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>139575346970</v>
+        <v>140566111020</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>우리로, 홀딩 및 상한가 기대감 속 외국인 순매수 신호와 개인 투자자들의 차익 실현.</t>
+          <t>우리로, 연말까지 홀딩 전략 속 급등 기대감. 외국인·프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['홀딩', '상한가', '외국인']</t>
+          <t>['홀딩', '급등 기대', '외국인 매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18870</v>
+        <v>18810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.99%</t>
+          <t>'+16.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="F4" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="G4" t="n">
-        <v>1752</v>
+        <v>1791</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -785,7 +785,7 @@
         <v>16360</v>
       </c>
       <c r="L4" t="n">
-        <v>18870</v>
+        <v>18970</v>
       </c>
       <c r="M4" t="n">
         <v>16170</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>635555572540</v>
+        <v>665056746885</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31400</v>
+        <v>12800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.95%</t>
+          <t>'+10.54%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.67</v>
       </c>
       <c r="E5" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="G5" t="n">
-        <v>185</v>
+        <v>515</v>
       </c>
       <c r="H5" t="n">
-        <v>11.44</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>28300</v>
+        <v>11580</v>
       </c>
       <c r="K5" t="n">
-        <v>28850</v>
+        <v>12200</v>
       </c>
       <c r="L5" t="n">
-        <v>32050</v>
+        <v>13820</v>
       </c>
       <c r="M5" t="n">
-        <v>28550</v>
+        <v>12100</v>
       </c>
       <c r="N5" t="n">
-        <v>11.46</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>172238248275</v>
+        <v>117506738800</v>
       </c>
       <c r="P5" t="n">
-        <v>75900</v>
+        <v>21150</v>
       </c>
       <c r="Q5" t="n">
-        <v>15000</v>
+        <v>8140</v>
       </c>
       <c r="R5" t="n">
-        <v>253000</v>
+        <v>483000</v>
       </c>
       <c r="S5" t="n">
-        <v>29000</v>
+        <v>107000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대한전선, 저평가 해소 및 박스권 상단 돌파 기대감 속 기관 순매수 신호.</t>
+          <t>파미셀, 모더나 관련 기대감 속 단기 급등 후 차익 실현 매물 출회. 투자자 혼조세.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['저평가', '박스권', '기관']</t>
+          <t>['모더나', '셀그램', '단타']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12730</v>
+        <v>31200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.93%</t>
+          <t>'+10.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.67</v>
+        <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F6" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>505</v>
+        <v>194</v>
       </c>
       <c r="H6" t="n">
-        <v>8.029999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11580</v>
+        <v>28300</v>
       </c>
       <c r="K6" t="n">
-        <v>12200</v>
+        <v>28850</v>
       </c>
       <c r="L6" t="n">
-        <v>13820</v>
+        <v>32050</v>
       </c>
       <c r="M6" t="n">
-        <v>12100</v>
+        <v>28550</v>
       </c>
       <c r="N6" t="n">
-        <v>8.699999999999999</v>
+        <v>11.46</v>
       </c>
       <c r="O6" t="n">
-        <v>116644681590</v>
+        <v>174345109900</v>
       </c>
       <c r="P6" t="n">
-        <v>21150</v>
+        <v>75900</v>
       </c>
       <c r="Q6" t="n">
-        <v>8140</v>
+        <v>15000</v>
       </c>
       <c r="R6" t="n">
-        <v>483000</v>
+        <v>253000</v>
       </c>
       <c r="S6" t="n">
-        <v>107000</v>
+        <v>29000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>파미셀, 모더나 관련 기대감 속 개인 투자자들의 엇갈린 전망과 투매 신호.</t>
+          <t>대한전선, 가온전선과의 비교 속 저평가 해소 기대감. 32000원 장기 박스권 상단 돌파 시도.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['셀그램', '투자전망', '주가']</t>
+          <t>['저평가 해소', '박스권 상단', '가온전선']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6410</v>
+        <v>13990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.01%</t>
+          <t>'+8.79%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H7" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5880</v>
+        <v>12860</v>
       </c>
       <c r="K7" t="n">
-        <v>5950</v>
+        <v>13020</v>
       </c>
       <c r="L7" t="n">
-        <v>6920</v>
+        <v>14230</v>
       </c>
       <c r="M7" t="n">
-        <v>5840</v>
+        <v>13000</v>
       </c>
       <c r="N7" t="n">
-        <v>1.83</v>
+        <v>2.83</v>
       </c>
       <c r="O7" t="n">
-        <v>84527837030</v>
+        <v>133246969895</v>
       </c>
       <c r="P7" t="n">
-        <v>11760</v>
+        <v>20300</v>
       </c>
       <c r="Q7" t="n">
-        <v>1620</v>
+        <v>2885</v>
       </c>
       <c r="R7" t="n">
-        <v>691000</v>
+        <v>150000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>KBI메탈, 변압기 관련주로서의 저평가 해소 및 전환사채 발행 후 상한가 기대감.</t>
+          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['변압기', '저평가', '전환사채']</t>
+          <t>['LA전력청', '매출', '테스트']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,91 +1103,91 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13970</v>
+        <v>6380</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.63%</t>
+          <t>'+8.50%</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E8" t="n">
+        <v>117</v>
+      </c>
+      <c r="F8" t="n">
+        <v>57</v>
+      </c>
+      <c r="G8" t="n">
+        <v>154</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5880</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5950</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6920</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5840</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O8" t="n">
+        <v>85298624015</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11760</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1620</v>
+      </c>
+      <c r="R8" t="n">
+        <v>691000</v>
+      </c>
+      <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>68</v>
-      </c>
-      <c r="F8" t="n">
-        <v>36</v>
-      </c>
-      <c r="G8" t="n">
-        <v>138</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>12860</v>
-      </c>
-      <c r="K8" t="n">
-        <v>13020</v>
-      </c>
-      <c r="L8" t="n">
-        <v>14230</v>
-      </c>
-      <c r="M8" t="n">
-        <v>13000</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O8" t="n">
-        <v>132006610955</v>
-      </c>
-      <c r="P8" t="n">
-        <v>20300</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2885</v>
-      </c>
-      <c r="R8" t="n">
-        <v>150000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>48000</v>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
+          <t>KBI메탈, 가온전선·대한전선 등 전력 관련주와 동반 상승 기대. 전환사채 발행 후에도 매수세 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LA전력청', '매출', '테스트']</t>
+          <t>['전력 관련주', '전환사채', '박스권 돌파']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1832000</v>
+        <v>1839000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.99%</t>
+          <t>'+5.39%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="G9" t="n">
-        <v>2273</v>
+        <v>2202</v>
       </c>
       <c r="H9" t="n">
         <v>50.1</v>
@@ -1245,7 +1245,7 @@
         <v>1810000</v>
       </c>
       <c r="L9" t="n">
-        <v>1833000</v>
+        <v>1840000</v>
       </c>
       <c r="M9" t="n">
         <v>1805000</v>
@@ -1254,7 +1254,7 @@
         <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2652074578500</v>
+        <v>2852103477000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 외인 순매수 전환 및 자사주 매입 시작에 따른 190만 돌파 기대감.</t>
+          <t>외국인 순매수 전환 및 자사주 매입 시작, 반도체 산업 전망 긍정론에 따른 상승 기대. 장기 투자 시 수익 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인매수', '자사주매입', '반도체']</t>
+          <t>['외국인 순매수', '자사주 매입', '반도체 전망']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,79 +1299,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13870</v>
+        <v>11110</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.05%</t>
+          <t>'+4.71%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>466</v>
+        <v>155</v>
       </c>
       <c r="H10" t="n">
-        <v>4.92</v>
+        <v>12.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13330</v>
+        <v>10610</v>
       </c>
       <c r="K10" t="n">
-        <v>13600</v>
+        <v>10730</v>
       </c>
       <c r="L10" t="n">
-        <v>14030</v>
+        <v>12390</v>
       </c>
       <c r="M10" t="n">
-        <v>13210</v>
+        <v>10510</v>
       </c>
       <c r="N10" t="n">
-        <v>4.99</v>
+        <v>12.6</v>
       </c>
       <c r="O10" t="n">
-        <v>53951808665</v>
+        <v>105184280330</v>
       </c>
       <c r="P10" t="n">
-        <v>30200</v>
+        <v>14350</v>
       </c>
       <c r="Q10" t="n">
-        <v>3540</v>
+        <v>465</v>
       </c>
       <c r="R10" t="n">
-        <v>68000</v>
+        <v>30000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
+          <t>금호전기, 전기 전선주 장세 속 프로그램 매수세 유입. 호남반도체 관련 기대감 속 혼조세.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미국원전주', '매물대', '목표가']</t>
+          <t>['전기 전선주', '프로그램 매수', '호남반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,43 +1379,43 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11040</v>
+        <v>260500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.05%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>443</v>
       </c>
       <c r="G11" t="n">
-        <v>133</v>
+        <v>2032</v>
       </c>
       <c r="H11" t="n">
-        <v>12.5</v>
+        <v>46.48</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10610</v>
+        <v>252500</v>
       </c>
       <c r="K11" t="n">
-        <v>10730</v>
+        <v>261000</v>
       </c>
       <c r="L11" t="n">
-        <v>12390</v>
+        <v>261000</v>
       </c>
       <c r="M11" t="n">
-        <v>10510</v>
+        <v>257500</v>
       </c>
       <c r="N11" t="n">
-        <v>12.6</v>
+        <v>46.52</v>
       </c>
       <c r="O11" t="n">
-        <v>102410846670</v>
+        <v>1572353289750</v>
       </c>
       <c r="P11" t="n">
-        <v>14350</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>465</v>
+        <v>78600</v>
       </c>
       <c r="R11" t="n">
-        <v>30000</v>
+        <v>-601000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주포 매수세 유입 및 호남반도체 관련 언급으로 상한가 기대감 형성. 전기·건설 테마주로 분류되며 프로그램 매수세 확인.</t>
+          <t>삼성전자, 정치적 발언이 주를 이루는 내용으로 특정 정치인에 대한 비판과 지지 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,143 +1463,143 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주포', '호남반도체', '상한가']</t>
+          <t>['정치', '기자회견', '대통령']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19070</v>
+        <v>13740</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.14%</t>
+          <t>'+3.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>349</v>
+        <v>481</v>
       </c>
       <c r="H12" t="n">
-        <v>10.74</v>
+        <v>4.92</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18490</v>
+        <v>13330</v>
       </c>
       <c r="K12" t="n">
-        <v>18900</v>
+        <v>13600</v>
       </c>
       <c r="L12" t="n">
-        <v>19700</v>
+        <v>14030</v>
       </c>
       <c r="M12" t="n">
-        <v>18770</v>
+        <v>13210</v>
       </c>
       <c r="N12" t="n">
-        <v>10.85</v>
+        <v>4.99</v>
       </c>
       <c r="O12" t="n">
-        <v>100261823355</v>
+        <v>55417154525</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>30200</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>3540</v>
       </c>
       <c r="R12" t="n">
-        <v>392000</v>
+        <v>68000</v>
       </c>
       <c r="S12" t="n">
-        <v>106000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국장 및 중동 정세 관련 상승 기대감. 대차해지 운동 참여 독려.</t>
+          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대차해지', '중동', '건설']</t>
+          <t>['미국원전주', '매물대', '목표가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>260000</v>
+        <v>18955</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.97%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>126</v>
       </c>
       <c r="F13" t="n">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>2049</v>
+        <v>379</v>
       </c>
       <c r="H13" t="n">
-        <v>46.48</v>
+        <v>10.74</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>252500</v>
+        <v>18490</v>
       </c>
       <c r="K13" t="n">
-        <v>261000</v>
+        <v>18900</v>
       </c>
       <c r="L13" t="n">
-        <v>261000</v>
+        <v>19700</v>
       </c>
       <c r="M13" t="n">
-        <v>257500</v>
+        <v>18770</v>
       </c>
       <c r="N13" t="n">
-        <v>46.52</v>
+        <v>10.85</v>
       </c>
       <c r="O13" t="n">
-        <v>1491682652250</v>
+        <v>104103471255</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>78600</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-601000</v>
+        <v>392000</v>
       </c>
       <c r="S13" t="n">
-        <v>333000</v>
+        <v>106000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성전자, 정치적 발언이 주를 이루는 내용으로 특정 정치인에 대한 비판과 지지 혼재.</t>
+          <t>대우건설, 미국장 원전주 상승세 및 중동 전쟁 관련 기대감. 대차해지 운동 참여 독려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '기자회견', '대통령']</t>
+          <t>['원전주', '대차해지', '중동 전쟁']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52600</v>
+        <v>52200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.94%</t>
+          <t>'+2.15%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="H14" t="n">
         <v>38.54</v>
@@ -1714,7 +1714,7 @@
         <v>38.62</v>
       </c>
       <c r="O14" t="n">
-        <v>189130780250</v>
+        <v>193678254250</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 외인·기관 동시 매수세 속 상승 기대감과 개인 투자자들의 매도 관망세.</t>
+          <t>삼성E&amp;A, 외인·기관 동시 매수세 유입 속 우상향 추세 기대. 52000원 돌파 시도.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인기관', '매수세', '상승전망']</t>
+          <t>['외인 기관 매수', '우상향', '매물 소화']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17540</v>
+        <v>17530</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+1.62%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H15" t="n">
         <v>0.97</v>
@@ -1806,7 +1806,7 @@
         <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>69732928295</v>
+        <v>70582613415</v>
       </c>
       <c r="P15" t="n">
         <v>30550</v>
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85600</v>
+        <v>18100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.95%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.04</v>
+        <v>0.38</v>
       </c>
       <c r="E16" t="n">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="F16" t="n">
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>981</v>
+        <v>290</v>
       </c>
       <c r="H16" t="n">
-        <v>23.23</v>
+        <v>0.98</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>85400</v>
+        <v>17930</v>
       </c>
       <c r="K16" t="n">
-        <v>87300</v>
+        <v>18400</v>
       </c>
       <c r="L16" t="n">
-        <v>87800</v>
+        <v>20400</v>
       </c>
       <c r="M16" t="n">
-        <v>85300</v>
+        <v>17670</v>
       </c>
       <c r="N16" t="n">
-        <v>23.27</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>83895128000</v>
+        <v>74365438305</v>
       </c>
       <c r="P16" t="n">
-        <v>139200</v>
+        <v>21100</v>
       </c>
       <c r="Q16" t="n">
-        <v>57000</v>
+        <v>9900</v>
       </c>
       <c r="R16" t="n">
-        <v>-206000</v>
+        <v>32000</v>
       </c>
       <c r="S16" t="n">
-        <v>-59000</v>
+        <v>22000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 미국 원전주 급등에 따른 대미 투자 관련 발표 기대감 및 긍정적 주가 흐름.</t>
+          <t>인제니아테라퓨틱스, 락업 해제 관련 우려 속 주가 변동성 확대. 기술이전 및 3상 결과 주목.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '대미투자', '주가흐름']</t>
+          <t>['락업 해제', '기술이전', '3상']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13380</v>
+        <v>13390</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.15%</t>
+          <t>'+0.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G17" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>35272198710</v>
+        <v>36324375820</v>
       </c>
       <c r="P17" t="n">
         <v>19380</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>호남반도체 관련 기대감 있으나, 실적 부진 및 급락 가능성에 대한 경고. 금호전기와의 비교 언급.</t>
+          <t>금호건설, 호남반도체 관련 기대감 속 혼조세. 실적 개선 및 주가 상승 여부에 대한 관망세.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['호남반도체', '실적', '급락']</t>
+          <t>['호남반도체', '실적 개선', '기자회견']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2035,70 +2035,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17920</v>
+        <v>85100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.38</v>
+        <v>-0.04</v>
       </c>
       <c r="E18" t="n">
+        <v>225</v>
+      </c>
+      <c r="F18" t="n">
         <v>131</v>
       </c>
-      <c r="F18" t="n">
-        <v>63</v>
-      </c>
       <c r="G18" t="n">
-        <v>284</v>
+        <v>1005</v>
       </c>
       <c r="H18" t="n">
-        <v>0.98</v>
+        <v>23.23</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17930</v>
+        <v>85400</v>
       </c>
       <c r="K18" t="n">
-        <v>18400</v>
+        <v>87300</v>
       </c>
       <c r="L18" t="n">
-        <v>20400</v>
+        <v>87800</v>
       </c>
       <c r="M18" t="n">
-        <v>17670</v>
+        <v>85100</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6</v>
+        <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>73653003550</v>
+        <v>93661031650</v>
       </c>
       <c r="P18" t="n">
-        <v>21100</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>9900</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>32000</v>
+        <v>-206000</v>
       </c>
       <c r="S18" t="n">
-        <v>22000</v>
+        <v>-59000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>락업 해제 물량 소화 중. 단기 급등보다는 긴 윗꼬리 패턴 반복.</t>
+          <t>미국 증시 원전주 급등 소식과 대미 투자 관련 발표 가능성으로 인한 상승 기대. 전력 부족 심화 뉴스 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['락업해제', '물량소화', '윗꼬리']</t>
+          <t>['원전주', '대미 투자', '전력 부족']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10240</v>
+        <v>10220</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.67%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>28540248590</v>
+        <v>29737870895</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4145</v>
+        <v>4185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-10.57%</t>
+          <t>'-9.71%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F20" t="n">
         <v>117</v>
       </c>
       <c r="G20" t="n">
-        <v>752</v>
+        <v>767</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2266,7 +2266,7 @@
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>33178513195</v>
+        <v>33679608900</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>

--- a/data/trending_integrated_20260918_12.xlsx
+++ b/data/trending_integrated_20260918_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26300</v>
+        <v>26250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.76%</t>
+          <t>'+21.53%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -601,7 +601,7 @@
         <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>26300</v>
+        <v>26550</v>
       </c>
       <c r="M2" t="n">
         <v>21700</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>262480817075</v>
+        <v>275824213875</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>성호전자, 박스권 상단 돌파 후 강한 상승세. 외인·프로그램 매수세 유입 속 대장주 역할 기대.</t>
+          <t>통신주 하락 속 외인 프로그램 매수세 유입에 따른 박스권 상단 돌파 및 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '외인 매수', '대장주']</t>
+          <t>['박스권 돌파', '외인 매수', '통신주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8300</v>
+        <v>8320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.23%</t>
+          <t>'+18.52%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>140566111020</v>
+        <v>141865824990</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>우리로, 연말까지 홀딩 전략 속 급등 기대감. 외국인·프로그램 매수세 유입.</t>
+          <t>단기 급등 후 조정 국면에서 평정심 유지 및 홀딩 전략 권고. 적정가 대비 저평가 논란과 함께 상한가 안착 기대감 공존. 매물대 부담 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['홀딩', '급등 기대', '외국인 매수']</t>
+          <t>['홀딩 전략', '적정가', '매물대 부담']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="F4" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G4" t="n">
-        <v>1791</v>
+        <v>1844</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>665056746885</v>
+        <v>674966468815</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>수익률 급등 및 2차 매물대 돌파 시도. 외인/기관/투신 매수세 유입 확인.</t>
+          <t>상승 추세 속에 외인/기관/투신 매수세 집중 확인. 2차 매물대 돌파 시도 및 숏커버링 발생. 역사적 신고가 경신 기대감 형성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['수익률', '매수세', '돌파']</t>
+          <t>['매수세 집중', '숏커버링', '역사적 신고가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12800</v>
+        <v>12830</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.54%</t>
+          <t>'+10.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.67</v>
       </c>
       <c r="E5" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G5" t="n">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="H5" t="n">
         <v>8.029999999999999</v>
@@ -886,7 +886,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>117506738800</v>
+        <v>117908556455</v>
       </c>
       <c r="P5" t="n">
         <v>21150</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>파미셀, 모더나 관련 기대감 속 단기 급등 후 차익 실현 매물 출회. 투자자 혼조세.</t>
+          <t>셀그램 관련 뉴스 기대감과 함께 외인/기관 동시 매수세 감지되나, 높은 목표가 제시와 매도 물량 출회로 단기 손실 우려. 추세 전환 여부 관망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['모더나', '셀그램', '단타']</t>
+          <t>['셀그램', '외인/기관 동시 매수', '단기 손실']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31200</v>
+        <v>31000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.25%</t>
+          <t>'+9.54%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F6" t="n">
         <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H6" t="n">
         <v>11.44</v>
@@ -978,7 +978,7 @@
         <v>11.46</v>
       </c>
       <c r="O6" t="n">
-        <v>174345109900</v>
+        <v>177487891525</v>
       </c>
       <c r="P6" t="n">
         <v>75900</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대한전선, 가온전선과의 비교 속 저평가 해소 기대감. 32000원 장기 박스권 상단 돌파 시도.</t>
+          <t>가온전선과의 비교 언급 속 저평가 해소 및 박스권 돌파 기대감 형성. 연기금 매수세 유입 확인. 단기 매물 소화 및 상승 추세 지속 여부 관망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가 해소', '박스권 상단', '가온전선']</t>
+          <t>['저평가 해소', '박스권 돌파', '연기금 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,79 +1023,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13990</v>
+        <v>6360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.79%</t>
+          <t>'+8.16%</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E7" t="n">
+        <v>119</v>
+      </c>
+      <c r="F7" t="n">
+        <v>57</v>
+      </c>
+      <c r="G7" t="n">
+        <v>164</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>5880</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5950</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6920</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5840</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O7" t="n">
+        <v>85656874495</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11760</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1620</v>
+      </c>
+      <c r="R7" t="n">
+        <v>691000</v>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>69</v>
-      </c>
-      <c r="F7" t="n">
-        <v>37</v>
-      </c>
-      <c r="G7" t="n">
-        <v>141</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>12860</v>
-      </c>
-      <c r="K7" t="n">
-        <v>13020</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14230</v>
-      </c>
-      <c r="M7" t="n">
-        <v>13000</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="O7" t="n">
-        <v>133246969895</v>
-      </c>
-      <c r="P7" t="n">
-        <v>20300</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2885</v>
-      </c>
-      <c r="R7" t="n">
-        <v>150000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>48000</v>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
+          <t>박스권 돌파 및 전환사채 발행 이슈 속 주가 상승 기대감 형성. 외국인 및 프로그램 매수세 유입 확인. 전력 관련주로서의 매력 부각.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['LA전력청', '매출', '테스트']</t>
+          <t>['박스권 돌파', '전환사채', '전력 관련주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,91 +1103,91 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6380</v>
+        <v>13905</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.50%</t>
+          <t>'+8.13%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
         <v>154</v>
       </c>
       <c r="H8" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5880</v>
+        <v>12860</v>
       </c>
       <c r="K8" t="n">
-        <v>5950</v>
+        <v>13020</v>
       </c>
       <c r="L8" t="n">
-        <v>6920</v>
+        <v>14230</v>
       </c>
       <c r="M8" t="n">
-        <v>5840</v>
+        <v>13000</v>
       </c>
       <c r="N8" t="n">
-        <v>1.83</v>
+        <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>85298624015</v>
+        <v>134317766540</v>
       </c>
       <c r="P8" t="n">
-        <v>11760</v>
+        <v>20300</v>
       </c>
       <c r="Q8" t="n">
-        <v>1620</v>
+        <v>2885</v>
       </c>
       <c r="R8" t="n">
-        <v>691000</v>
+        <v>150000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>KBI메탈, 가온전선·대한전선 등 전력 관련주와 동반 상승 기대. 전환사채 발행 후에도 매수세 유입.</t>
+          <t>미주 매출 3.5배 폭증 및 제품 테스트 완료 소식 기반 수조원 미국 LA 전력청 계약 기대감. 전선·전력설비 테마주로 분류.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['전력 관련주', '전환사채', '박스권 돌파']</t>
+          <t>['LA전력청', '매출', '테스트']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1839000</v>
+        <v>1838000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.39%</t>
+          <t>'+5.33%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G9" t="n">
-        <v>2202</v>
+        <v>2221</v>
       </c>
       <c r="H9" t="n">
         <v>50.1</v>
@@ -1245,7 +1245,7 @@
         <v>1810000</v>
       </c>
       <c r="L9" t="n">
-        <v>1840000</v>
+        <v>1841000</v>
       </c>
       <c r="M9" t="n">
         <v>1805000</v>
@@ -1254,7 +1254,7 @@
         <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2852103477000</v>
+        <v>2991710152500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외국인 순매수 전환 및 자사주 매입 시작, 반도체 산업 전망 긍정론에 따른 상승 기대. 장기 투자 시 수익 가능성 언급.</t>
+          <t>외인 순매수 전환 및 자사주 매입 시작에 따른 200만 돌파 기대감 고조. 반도체 업황 안정 및 금리, 환율 등 거시 경제 지표 안정화 속 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '자사주 매입', '반도체 전망']</t>
+          <t>['외인 순매수', '자사주 매입', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11110</v>
+        <v>11130</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.71%</t>
+          <t>'+4.90%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H10" t="n">
         <v>12.5</v>
@@ -1346,7 +1346,7 @@
         <v>12.6</v>
       </c>
       <c r="O10" t="n">
-        <v>105184280330</v>
+        <v>106694288845</v>
       </c>
       <c r="P10" t="n">
         <v>14350</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>금호전기, 전기 전선주 장세 속 프로그램 매수세 유입. 호남반도체 관련 기대감 속 혼조세.</t>
+          <t>오전 분위기 상승 후 외국인 매수에 대한 기대감 있었으나, 호남반도체 관련 기대감 소멸로 주가 상승 여력 감소. 전기 전선주 장세 속 프로그램 매매 혼조.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['전기 전선주', '프로그램 매수', '호남반도체']</t>
+          <t>['호남반도체', '전기 전선주', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>260500</v>
+        <v>13780</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.17%</t>
+          <t>'+3.38%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>443</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>2032</v>
+        <v>490</v>
       </c>
       <c r="H11" t="n">
-        <v>46.48</v>
+        <v>4.92</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>252500</v>
+        <v>13330</v>
       </c>
       <c r="K11" t="n">
-        <v>261000</v>
+        <v>13600</v>
       </c>
       <c r="L11" t="n">
-        <v>261000</v>
+        <v>14030</v>
       </c>
       <c r="M11" t="n">
-        <v>257500</v>
+        <v>13210</v>
       </c>
       <c r="N11" t="n">
-        <v>46.52</v>
+        <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>1572353289750</v>
+        <v>56210195705</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>30200</v>
       </c>
       <c r="Q11" t="n">
-        <v>78600</v>
+        <v>3540</v>
       </c>
       <c r="R11" t="n">
-        <v>-601000</v>
+        <v>68000</v>
       </c>
       <c r="S11" t="n">
-        <v>333000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성전자, 정치적 발언이 주를 이루는 내용으로 특정 정치인에 대한 비판과 지지 혼재.</t>
+          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,90 +1463,90 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '기자회견', '대통령']</t>
+          <t>['미국원전주', '매물대', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13740</v>
+        <v>260000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.08%</t>
+          <t>'+2.97%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>441</v>
       </c>
       <c r="G12" t="n">
-        <v>481</v>
+        <v>2028</v>
       </c>
       <c r="H12" t="n">
-        <v>4.92</v>
+        <v>46.48</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13330</v>
+        <v>252500</v>
       </c>
       <c r="K12" t="n">
-        <v>13600</v>
+        <v>261000</v>
       </c>
       <c r="L12" t="n">
-        <v>14030</v>
+        <v>261000</v>
       </c>
       <c r="M12" t="n">
-        <v>13210</v>
+        <v>257500</v>
       </c>
       <c r="N12" t="n">
-        <v>4.99</v>
+        <v>46.52</v>
       </c>
       <c r="O12" t="n">
-        <v>55417154525</v>
+        <v>1625265049000</v>
       </c>
       <c r="P12" t="n">
-        <v>30200</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3540</v>
+        <v>78600</v>
       </c>
       <c r="R12" t="n">
-        <v>68000</v>
+        <v>-601000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>333000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 원전주 동반 상승에 따른 우리기술의 상승 기대감. 다음 주 목표가 15680원 제시 및 매물대 돌파 시 2만원 목표.</t>
+          <t>주요 게시글은 정치 관련 비판 및 논쟁으로, 삼성전자 주가와 직접적인 연관성 없는 내용 다수. 대통령 및 정치인 관련 비난 여론.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,20 +1555,20 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미국원전주', '매물대', '목표가']</t>
+          <t>['정치 비판', '이재명', '기자회견']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18955</v>
+        <v>18950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+2.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.85</v>
       </c>
       <c r="O13" t="n">
-        <v>104103471255</v>
+        <v>105987666145</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대우건설, 미국장 원전주 상승세 및 중동 전쟁 관련 기대감. 대차해지 운동 참여 독려.</t>
+          <t>미국 원전주 상승세와 연계된 기대감 속 대차해지 운동 참여 독려. 수주 발표 이후 주가 하락에 대한 의문 제기 및 중동 전쟁 종전 후 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전주', '대차해지', '중동 전쟁']</t>
+          <t>['원전주', '대차해지', '수주 발표']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>-0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G14" t="n">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="H14" t="n">
         <v>38.54</v>
@@ -1714,7 +1714,7 @@
         <v>38.62</v>
       </c>
       <c r="O14" t="n">
-        <v>193678254250</v>
+        <v>199114984400</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 외인·기관 동시 매수세 유입 속 우상향 추세 기대. 52000원 돌파 시도.</t>
+          <t>주가 상승에 대한 기대감과 함께 외인/기관의 집중 매수세 확인. 물량 소화 및 우상향 추세 전망. 일부 매물대 소화 과정 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['외인 기관 매수', '우상향', '매물 소화']</t>
+          <t>['외인/기관 매수', '우상향 추세', '물량 소화']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17530</v>
+        <v>17490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.62%</t>
+          <t>'+1.39%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H15" t="n">
         <v>0.97</v>
@@ -1806,7 +1806,7 @@
         <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>70582613415</v>
+        <v>71099503035</v>
       </c>
       <c r="P15" t="n">
         <v>30550</v>
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18100</v>
+        <v>13460</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.95%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="H16" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17930</v>
+        <v>13360</v>
       </c>
       <c r="K16" t="n">
-        <v>18400</v>
+        <v>13450</v>
       </c>
       <c r="L16" t="n">
-        <v>20400</v>
+        <v>14450</v>
       </c>
       <c r="M16" t="n">
-        <v>17670</v>
+        <v>13350</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>74365438305</v>
+        <v>36790544000</v>
       </c>
       <c r="P16" t="n">
-        <v>21100</v>
+        <v>19380</v>
       </c>
       <c r="Q16" t="n">
-        <v>9900</v>
+        <v>3200</v>
       </c>
       <c r="R16" t="n">
-        <v>32000</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스, 락업 해제 관련 우려 속 주가 변동성 확대. 기술이전 및 3상 결과 주목.</t>
+          <t>호남반도체 관련 기대감과 함께 주가 급등 기대 있었으나, 관련 내용 부재로 인한 실망감 표출. 과거 명성 회복 및 실적 개선 여부 불확실.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['락업 해제', '기술이전', '3상']</t>
+          <t>['호남반도체', '실적 개선', '주가 급등 기대']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13390</v>
+        <v>17990</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.22%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="F17" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13360</v>
+        <v>17930</v>
       </c>
       <c r="K17" t="n">
-        <v>13450</v>
+        <v>18400</v>
       </c>
       <c r="L17" t="n">
-        <v>14450</v>
+        <v>20400</v>
       </c>
       <c r="M17" t="n">
-        <v>13350</v>
+        <v>17670</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>36324375820</v>
+        <v>74964780980</v>
       </c>
       <c r="P17" t="n">
-        <v>19380</v>
+        <v>21100</v>
       </c>
       <c r="Q17" t="n">
-        <v>3200</v>
+        <v>9900</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>32000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>금호건설, 호남반도체 관련 기대감 속 혼조세. 실적 개선 및 주가 상승 여부에 대한 관망세.</t>
+          <t>인제니아테라퓨틱스, 락업 해제 관련 우려 속 주가 변동성 확대. 기술이전 및 3상 결과 주목.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['호남반도체', '실적 개선', '기자회견']</t>
+          <t>['락업 해제', '기술이전', '3상']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85100</v>
+        <v>85350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="F18" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G18" t="n">
-        <v>1005</v>
+        <v>1037</v>
       </c>
       <c r="H18" t="n">
         <v>23.23</v>
@@ -2082,7 +2082,7 @@
         <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>93661031650</v>
+        <v>95901638300</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10220</v>
+        <v>10160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.67%</t>
+          <t>'-3.24%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>29737870895</v>
+        <v>30417386865</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4185</v>
+        <v>4205</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.71%</t>
+          <t>'-9.28%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F20" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G20" t="n">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2266,7 +2266,7 @@
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>33679608900</v>
+        <v>34018458900</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-30.23%</t>
+          <t>'-37.21%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>
@@ -2358,7 +2358,7 @@
         <v>3.71</v>
       </c>
       <c r="O21" t="n">
-        <v>147161603</v>
+        <v>156074357</v>
       </c>
       <c r="P21" t="n">
         <v>901</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>K-OTC 시장에서의 원풍물산 주가 하락 지속. 대주주 지분 관련 및 기술 개발 협력 사실 언급에도 불구하고 투자 심리 위축.</t>
+          <t>K-OTC 장외 거래에 대한 회의적인 시각과 함께 대주주 변경 및 지분 관련 불확실성 존재. 신규 기술 개발 및 투자사 관심에도 불구하고 주가 하락 지속.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['K-OTC', '대주주', '기술개발']</t>
+          <t>['K-OTC', '상폐', '지분']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">

--- a/data/trending_integrated_20260918_12.xlsx
+++ b/data/trending_integrated_20260918_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26250</v>
+        <v>26625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+21.53%</t>
+          <t>'+23.26%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -601,7 +601,7 @@
         <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>26550</v>
+        <v>26650</v>
       </c>
       <c r="M2" t="n">
         <v>21700</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>275824213875</v>
+        <v>282106532700</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8320</v>
+        <v>8290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.52%</t>
+          <t>'+18.09%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>141865824990</v>
+        <v>142590966565</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>단기 급등 후 조정 국면에서 평정심 유지 및 홀딩 전략 권고. 적정가 대비 저평가 논란과 함께 상한가 안착 기대감 공존. 매물대 부담 관찰.</t>
+          <t>연말까지 홀딩 의견 및 10,000원 돌파 기대감 속, 외국인/프라이빗 매수 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['홀딩 전략', '적정가', '매물대 부담']</t>
+          <t>['홀딩', '외국인 매수', '상승 기대']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18810</v>
+        <v>18940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.62%</t>
+          <t>'+17.42%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="F4" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G4" t="n">
-        <v>1844</v>
+        <v>1971</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>674966468815</v>
+        <v>692809977410</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>상승 추세 속에 외인/기관/투신 매수세 집중 확인. 2차 매물대 돌파 시도 및 숏커버링 발생. 역사적 신고가 경신 기대감 형성.</t>
+          <t>외인/기관 투신 매수세 유입 및 숏커버링 발생으로 인한 급등세. 20,000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['매수세 집중', '숏커버링', '역사적 신고가']</t>
+          <t>['숏커버링', '외인/기관 매수', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12830</v>
+        <v>12790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.79%</t>
+          <t>'+10.45%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.67</v>
       </c>
       <c r="E5" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>524</v>
+        <v>582</v>
       </c>
       <c r="H5" t="n">
         <v>8.029999999999999</v>
@@ -886,7 +886,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>117908556455</v>
+        <v>118240487085</v>
       </c>
       <c r="P5" t="n">
         <v>21150</v>
@@ -946,13 +946,13 @@
         <v>-0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H6" t="n">
         <v>11.44</v>
@@ -978,7 +978,7 @@
         <v>11.46</v>
       </c>
       <c r="O6" t="n">
-        <v>177487891525</v>
+        <v>180582208375</v>
       </c>
       <c r="P6" t="n">
         <v>75900</v>
@@ -1038,13 +1038,13 @@
         <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H7" t="n">
         <v>2.85</v>
@@ -1070,7 +1070,7 @@
         <v>1.83</v>
       </c>
       <c r="O7" t="n">
-        <v>85656874495</v>
+        <v>86074659650</v>
       </c>
       <c r="P7" t="n">
         <v>11760</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>박스권 돌파 및 전환사채 발행 이슈 속 주가 상승 기대감 형성. 외국인 및 프로그램 매수세 유입 확인. 전력 관련주로서의 매력 부각.</t>
+          <t>전력 및 변압기 테마 강세 속, 박스권 돌파 및 전환사채 발행 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '전환사채', '전력 관련주']</t>
+          <t>['전력주', '변압기', '전환사채']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13905</v>
+        <v>13860</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.13%</t>
+          <t>'+7.78%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>134317766540</v>
+        <v>136225172875</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="G9" t="n">
-        <v>2221</v>
+        <v>2195</v>
       </c>
       <c r="H9" t="n">
         <v>50.1</v>
@@ -1254,7 +1254,7 @@
         <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2991710152500</v>
+        <v>3114542078500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 순매수 전환 및 자사주 매입 시작에 따른 200만 돌파 기대감 고조. 반도체 업황 안정 및 금리, 환율 등 거시 경제 지표 안정화 속 상승 추세 전망.</t>
+          <t>외인 순매수 전환 및 자사주 매입 시작으로 인한 상승 기대감, 200만 돌파 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 순매수', '자사주 매입', '반도체']</t>
+          <t>['외인 순매수', '자사주 매입', '목표가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11130</v>
+        <v>11020</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.90%</t>
+          <t>'+3.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H10" t="n">
         <v>12.5</v>
@@ -1346,7 +1346,7 @@
         <v>12.6</v>
       </c>
       <c r="O10" t="n">
-        <v>106694288845</v>
+        <v>109195238335</v>
       </c>
       <c r="P10" t="n">
         <v>14350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>오전 분위기 상승 후 외국인 매수에 대한 기대감 있었으나, 호남반도체 관련 기대감 소멸로 주가 상승 여력 감소. 전기 전선주 장세 속 프로그램 매매 혼조.</t>
+          <t>호남 반도체 관련 기대감에도 불구하고, 기자회견 내용 부재 및 프로그램 매수/매도 혼조세로 인한 불확실성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['호남반도체', '전기 전선주', '프로그램 매매']</t>
+          <t>['호남 반도체', '기자회견', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13780</v>
+        <v>13770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.38%</t>
+          <t>'+3.30%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
         <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="H11" t="n">
         <v>4.92</v>
@@ -1438,7 +1438,7 @@
         <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>56210195705</v>
+        <v>56816575660</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G12" t="n">
-        <v>2028</v>
+        <v>2012</v>
       </c>
       <c r="H12" t="n">
         <v>46.48</v>
@@ -1530,7 +1530,7 @@
         <v>46.52</v>
       </c>
       <c r="O12" t="n">
-        <v>1625265049000</v>
+        <v>1687448798500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주요 게시글은 정치 관련 비판 및 논쟁으로, 삼성전자 주가와 직접적인 연관성 없는 내용 다수. 대통령 및 정치인 관련 비난 여론.</t>
+          <t>대통령 기자회견 내용에 대한 불만 및 정치적 이슈 부각.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치 비판', '이재명', '기자회견']</t>
+          <t>['기자회견', '정치', '신뢰']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18950</v>
+        <v>18795</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.49%</t>
+          <t>'+1.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F13" t="n">
         <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.85</v>
       </c>
       <c r="O13" t="n">
-        <v>105987666145</v>
+        <v>109446150255</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 원전주 상승세와 연계된 기대감 속 대차해지 운동 참여 독려. 수주 발표 이후 주가 하락에 대한 의문 제기 및 중동 전쟁 종전 후 전망.</t>
+          <t>미국장 원전주 상승세 및 중동 전쟁 종전 논의 관련 기대감, 대차해지 운동 전개.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전주', '대차해지', '수주 발표']</t>
+          <t>['원전', '중동 전쟁', '대차해지']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52200</v>
+        <v>51900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.15%</t>
+          <t>'+1.57%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G14" t="n">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="H14" t="n">
         <v>38.54</v>
@@ -1714,7 +1714,7 @@
         <v>38.62</v>
       </c>
       <c r="O14" t="n">
-        <v>199114984400</v>
+        <v>201510965150</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17490</v>
+        <v>17500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.39%</t>
+          <t>'+1.45%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F15" t="n">
         <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H15" t="n">
         <v>0.97</v>
@@ -1806,7 +1806,7 @@
         <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>71099503035</v>
+        <v>71356659925</v>
       </c>
       <c r="P15" t="n">
         <v>30550</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미증시 양자컴퓨터 주식 급등에 따른 관련주 동반 상승 기대감. 단기 과열 우려 및 개인 투자자 포지션에 대한 언급.</t>
+          <t>미국 양자컴퓨터주 급등에 따른 기대감, AI/양자/보안 테마 관심.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['양자컴퓨터', '보안주', 'AI 반도체']</t>
+          <t>['양자컴퓨터', 'AI', '보안']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13460</v>
+        <v>13370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.75%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         <v>14450</v>
       </c>
       <c r="M16" t="n">
-        <v>13350</v>
+        <v>13310</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>36790544000</v>
+        <v>37762364985</v>
       </c>
       <c r="P16" t="n">
         <v>19380</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17990</v>
+        <v>17910</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'-0.11%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="H17" t="n">
         <v>0.98</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>74964780980</v>
+        <v>75295478780</v>
       </c>
       <c r="P17" t="n">
         <v>21100</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스, 락업 해제 관련 우려 속 주가 변동성 확대. 기술이전 및 3상 결과 주목.</t>
+          <t>락업 해제 물량 소화 과정 및 지속적인 매도 물량 출회로 인한 하락세.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['락업 해제', '기술이전', '3상']</t>
+          <t>['락업 해제', '매도 물량', '하락세']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85350</v>
+        <v>85100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F18" t="n">
         <v>132</v>
       </c>
       <c r="G18" t="n">
-        <v>1037</v>
+        <v>1087</v>
       </c>
       <c r="H18" t="n">
         <v>23.23</v>
@@ -2082,7 +2082,7 @@
         <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>95901638300</v>
+        <v>98505329200</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 증시 원전주 급등 소식과 대미 투자 관련 발표 가능성으로 인한 상승 기대. 전력 부족 심화 뉴스 언급.</t>
+          <t>미국 원전주 급등 및 대미 투자 발표 가능성 언급. 120일선 돌파 기대감 형성.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전주', '대미 투자', '전력 부족']</t>
+          <t>['원전주', '대미 투자', '120일선']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10160</v>
+        <v>10190</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.24%</t>
+          <t>'-2.95%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>30417386865</v>
+        <v>30733124075</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4205</v>
+        <v>4175</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.28%</t>
+          <t>'-9.92%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F20" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G20" t="n">
-        <v>782</v>
+        <v>805</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2266,7 +2266,7 @@
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>34018458900</v>
+        <v>34460635140</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>STO 사업 추진 및 스테이블코인 테마 기대감 속 급락. 주포 매도세 관측.</t>
+          <t>STO 사업 추진 및 미국 코인 주식거래 허용 관련 호재, 스테이블코인 테마 편입 가능성.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['STO', '스테이블코인', '매도세']</t>
+          <t>['STO', '암호화폐', '스테이블코인']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>

--- a/data/trending_integrated_20260918_12.xlsx
+++ b/data/trending_integrated_20260918_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26625</v>
+        <v>26850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.26%</t>
+          <t>'+24.31%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="H2" t="n">
         <v>2.41</v>
@@ -601,7 +601,7 @@
         <v>22250</v>
       </c>
       <c r="L2" t="n">
-        <v>26650</v>
+        <v>26850</v>
       </c>
       <c r="M2" t="n">
         <v>21700</v>
@@ -610,7 +610,7 @@
         <v>2.61</v>
       </c>
       <c r="O2" t="n">
-        <v>282106532700</v>
+        <v>292082236300</v>
       </c>
       <c r="P2" t="n">
         <v>59600</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>통신주 하락 속 외인 프로그램 매수세 유입에 따른 박스권 상단 돌파 및 추가 상승 기대.</t>
+          <t>통신주 장세 속 프로그램 매수세 집중 및 외인 폭풍 매수. 5~6만원대 재진입 기대감과 함께 대장주로서의 흐름 관측.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['박스권 돌파', '외인 매수', '통신주']</t>
+          <t>['통신주', '프로그램매수', '외인매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8290</v>
+        <v>8260</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.09%</t>
+          <t>'+17.66%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.59</v>
       </c>
       <c r="O3" t="n">
-        <v>142590966565</v>
+        <v>143512533250</v>
       </c>
       <c r="P3" t="n">
         <v>16200</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>연말까지 홀딩 의견 및 10,000원 돌파 기대감 속, 외국인/프라이빗 매수 관찰.</t>
+          <t>연말까지 홀딩 의견 및 상한가 기대감 표출. 다만, 변동성 심화와 매물대 부담으로 인한 하락세 관측.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['홀딩', '외국인 매수', '상승 기대']</t>
+          <t>['홀딩', '변동성', '매물대']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18940</v>
+        <v>18830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.42%</t>
+          <t>'+16.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="F4" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G4" t="n">
-        <v>1971</v>
+        <v>2188</v>
       </c>
       <c r="H4" t="n">
         <v>4.61</v>
@@ -785,7 +785,7 @@
         <v>16360</v>
       </c>
       <c r="L4" t="n">
-        <v>18970</v>
+        <v>18990</v>
       </c>
       <c r="M4" t="n">
         <v>16170</v>
@@ -794,7 +794,7 @@
         <v>4.88</v>
       </c>
       <c r="O4" t="n">
-        <v>692809977410</v>
+        <v>708268471805</v>
       </c>
       <c r="P4" t="n">
         <v>31500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외인/기관 투신 매수세 유입 및 숏커버링 발생으로 인한 급등세. 20,000원 돌파 기대.</t>
+          <t>외인/기관 동시 매수세 확인된 가운데 2차 매물대 돌파 시도. 숏커버링 발생 및 20,000원 돌파 기대감 고조.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['숏커버링', '외인/기관 매수', '급등']</t>
+          <t>['외인기관', '매물대돌파', '숏커버링']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12790</v>
+        <v>31200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.45%</t>
+          <t>'+10.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.67</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>582</v>
+        <v>190</v>
       </c>
       <c r="H5" t="n">
-        <v>8.029999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11580</v>
+        <v>28300</v>
       </c>
       <c r="K5" t="n">
-        <v>12200</v>
+        <v>28850</v>
       </c>
       <c r="L5" t="n">
-        <v>13820</v>
+        <v>32050</v>
       </c>
       <c r="M5" t="n">
-        <v>12100</v>
+        <v>28550</v>
       </c>
       <c r="N5" t="n">
-        <v>8.699999999999999</v>
+        <v>11.46</v>
       </c>
       <c r="O5" t="n">
-        <v>118240487085</v>
+        <v>182364493150</v>
       </c>
       <c r="P5" t="n">
-        <v>21150</v>
+        <v>75900</v>
       </c>
       <c r="Q5" t="n">
-        <v>8140</v>
+        <v>15000</v>
       </c>
       <c r="R5" t="n">
-        <v>483000</v>
+        <v>253000</v>
       </c>
       <c r="S5" t="n">
-        <v>107000</v>
+        <v>29000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>셀그램 관련 뉴스 기대감과 함께 외인/기관 동시 매수세 감지되나, 높은 목표가 제시와 매도 물량 출회로 단기 손실 우려. 추세 전환 여부 관망.</t>
+          <t>가온전선과의 비교 속 저평가 해소 기대감 형성. 프로그램 매수세와 함께 추세 전환 가능성 탐색.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['셀그램', '외인/기관 동시 매수', '단기 손실']</t>
+          <t>['저평가', '가온전선', '프로그램매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31000</v>
+        <v>12710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.54%</t>
+          <t>'+9.76%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.02</v>
+        <v>-0.67</v>
       </c>
       <c r="E6" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="G6" t="n">
-        <v>190</v>
+        <v>584</v>
       </c>
       <c r="H6" t="n">
-        <v>11.44</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>28300</v>
+        <v>11580</v>
       </c>
       <c r="K6" t="n">
-        <v>28850</v>
+        <v>12200</v>
       </c>
       <c r="L6" t="n">
-        <v>32050</v>
+        <v>13820</v>
       </c>
       <c r="M6" t="n">
-        <v>28550</v>
+        <v>12100</v>
       </c>
       <c r="N6" t="n">
-        <v>11.46</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>180582208375</v>
+        <v>118828060475</v>
       </c>
       <c r="P6" t="n">
-        <v>75900</v>
+        <v>21150</v>
       </c>
       <c r="Q6" t="n">
-        <v>15000</v>
+        <v>8140</v>
       </c>
       <c r="R6" t="n">
-        <v>253000</v>
+        <v>483000</v>
       </c>
       <c r="S6" t="n">
-        <v>29000</v>
+        <v>107000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 언급 속 저평가 해소 및 박스권 돌파 기대감 형성. 연기금 매수세 유입 확인. 단기 매물 소화 및 상승 추세 지속 여부 관망.</t>
+          <t>셀그램 관련 뉴스 기대감 속 외인/기관 동시 매수세 관측. 그러나 높은 변동성과 일부 투자자 손실 발생으로 향후 전망 불확실.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가 해소', '박스권 돌파', '연기금 매수']</t>
+          <t>['셀그램', '외인기관', '변동성']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6360</v>
+        <v>6390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.16%</t>
+          <t>'+8.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
         <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H7" t="n">
         <v>2.85</v>
@@ -1070,7 +1070,7 @@
         <v>1.83</v>
       </c>
       <c r="O7" t="n">
-        <v>86074659650</v>
+        <v>86475850080</v>
       </c>
       <c r="P7" t="n">
         <v>11760</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>전력 및 변압기 테마 강세 속, 박스권 돌파 및 전환사채 발행 기대감.</t>
+          <t>전환사채 발행 이후 박스권 돌파 및 전력/변압기 관련주 주목. 외국인/프로그램 매수세 유입으로 인한 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전력주', '변압기', '전환사채']</t>
+          <t>['전환사채', '박스권돌파', '외국인매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13860</v>
+        <v>13900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.78%</t>
+          <t>'+8.09%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H8" t="n">
         <v>2.83</v>
@@ -1162,7 +1162,7 @@
         <v>2.83</v>
       </c>
       <c r="O8" t="n">
-        <v>136225172875</v>
+        <v>137568228310</v>
       </c>
       <c r="P8" t="n">
         <v>20300</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1838000</v>
+        <v>1843000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.33%</t>
+          <t>'+5.62%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="G9" t="n">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="H9" t="n">
         <v>50.1</v>
@@ -1245,7 +1245,7 @@
         <v>1810000</v>
       </c>
       <c r="L9" t="n">
-        <v>1841000</v>
+        <v>1844000</v>
       </c>
       <c r="M9" t="n">
         <v>1805000</v>
@@ -1254,7 +1254,7 @@
         <v>50.2</v>
       </c>
       <c r="O9" t="n">
-        <v>3114542078500</v>
+        <v>3224501783500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 순매수 전환 및 자사주 매입 시작으로 인한 상승 기대감, 200만 돌파 전망.</t>
+          <t>외인 순매수 전환 및 자사주 매입 시작 소식에 따른 195만원 이상 목표 주가 기대감 형성. 장기 투자 시 수익 증대 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 순매수', '자사주 매입', '목표가']</t>
+          <t>['외인 순매수', '자사주 매입', '목표 주가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11020</v>
+        <v>11070</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.86%</t>
+          <t>'+4.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G10" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H10" t="n">
         <v>12.5</v>
@@ -1346,7 +1346,7 @@
         <v>12.6</v>
       </c>
       <c r="O10" t="n">
-        <v>109195238335</v>
+        <v>110760377860</v>
       </c>
       <c r="P10" t="n">
         <v>14350</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>호남 반도체 관련 기대감에도 불구하고, 기자회견 내용 부재 및 프로그램 매수/매도 혼조세로 인한 불확실성.</t>
+          <t>호남 반도체 관련 기대감과 함께 전기/전선주 장세 속 프로그램 매수세 유입. 하지만 관련 이슈 불확실성으로 주가 변동성 관측.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['호남 반도체', '기자회견', '프로그램 매매']</t>
+          <t>['호남반도체', '전기전선주', '프로그램매매']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13770</v>
+        <v>13760</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.30%</t>
+          <t>'+3.23%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="H11" t="n">
         <v>4.92</v>
@@ -1438,7 +1438,7 @@
         <v>4.99</v>
       </c>
       <c r="O11" t="n">
-        <v>56816575660</v>
+        <v>57677525540</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>260000</v>
+        <v>260500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.97%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="G12" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H12" t="n">
         <v>46.48</v>
@@ -1530,7 +1530,7 @@
         <v>46.52</v>
       </c>
       <c r="O12" t="n">
-        <v>1687448798500</v>
+        <v>1758621696000</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대통령 기자회견 내용에 대한 불만 및 정치적 이슈 부각.</t>
+          <t>정치적 논쟁 및 기자회견에 대한 부정적 의견 표출. 주가 관련 분석이나 팩트 기반 내용은 부재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['기자회견', '정치', '신뢰']</t>
+          <t>['정치', '기자회견', '논쟁']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18795</v>
+        <v>18890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.65%</t>
+          <t>'+2.16%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1616,13 +1616,13 @@
         <v>19700</v>
       </c>
       <c r="M13" t="n">
-        <v>18770</v>
+        <v>18760</v>
       </c>
       <c r="N13" t="n">
         <v>10.85</v>
       </c>
       <c r="O13" t="n">
-        <v>109446150255</v>
+        <v>112413838135</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51900</v>
+        <v>52200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.57%</t>
+          <t>'+2.15%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F14" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="H14" t="n">
         <v>38.54</v>
@@ -1714,7 +1714,7 @@
         <v>38.62</v>
       </c>
       <c r="O14" t="n">
-        <v>201510965150</v>
+        <v>203584134600</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17500</v>
+        <v>17600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.45%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F15" t="n">
         <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H15" t="n">
         <v>0.97</v>
@@ -1806,7 +1806,7 @@
         <v>0.7</v>
       </c>
       <c r="O15" t="n">
-        <v>71356659925</v>
+        <v>71734163455</v>
       </c>
       <c r="P15" t="n">
         <v>30550</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13370</v>
+        <v>13400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
         <v>289</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>37762364985</v>
+        <v>38251884775</v>
       </c>
       <c r="P16" t="n">
         <v>19380</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>호남반도체 관련 기대감과 함께 주가 급등 기대 있었으나, 관련 내용 부재로 인한 실망감 표출. 과거 명성 회복 및 실적 개선 여부 불확실.</t>
+          <t>호남 반도체 관련 이슈 재점화 기대 속 실적 개선 전망. 그러나 관련 뉴스 부재 및 주가 하락 우려 공존.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['호남반도체', '실적 개선', '주가 급등 기대']</t>
+          <t>['호남반도체', '실적개선', '이슈']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17910</v>
+        <v>17980</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.11%</t>
+          <t>'+0.28%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.38</v>
       </c>
       <c r="E17" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F17" t="n">
         <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="H17" t="n">
         <v>0.98</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>75295478780</v>
+        <v>75632843520</v>
       </c>
       <c r="P17" t="n">
         <v>21100</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>락업 해제 물량 소화 과정 및 지속적인 매도 물량 출회로 인한 하락세.</t>
+          <t>락업 해제 물량 소화 과정 속 주가 변동성 심화. 목표가 5만원 제시되나, 단기 급등보다는 긴 윗꼬리 패턴 반복 경계.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['락업 해제', '매도 물량', '하락세']</t>
+          <t>['락업해제', '변동성', '윗꼬리']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85100</v>
+        <v>85400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F18" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G18" t="n">
-        <v>1087</v>
+        <v>1121</v>
       </c>
       <c r="H18" t="n">
         <v>23.23</v>
@@ -2082,7 +2082,7 @@
         <v>23.27</v>
       </c>
       <c r="O18" t="n">
-        <v>98505329200</v>
+        <v>100660012250</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2142,13 +2142,13 @@
         <v>-0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F19" t="n">
         <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H19" t="n">
         <v>1.24</v>
@@ -2174,7 +2174,7 @@
         <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>30733124075</v>
+        <v>30970925420</v>
       </c>
       <c r="P19" t="n">
         <v>15960</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4175</v>
+        <v>4155</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-9.92%</t>
+          <t>'-10.36%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.4</v>
       </c>
       <c r="E20" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F20" t="n">
         <v>122</v>
       </c>
       <c r="G20" t="n">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="H20" t="n">
         <v>0.55</v>
@@ -2266,7 +2266,7 @@
         <v>0.95</v>
       </c>
       <c r="O20" t="n">
-        <v>34460635140</v>
+        <v>34902739841</v>
       </c>
       <c r="P20" t="n">
         <v>6900</v>
@@ -2326,13 +2326,13 @@
         <v>-0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F21" t="n">
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H21" t="n">
         <v>3.69</v>
